--- a/backtest_runs/20260410_193731/by_symbol/DFSM/DFSM.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/DFSM/DFSM.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         <v>-6641.25000000001</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>102466.75</v>
@@ -679,7 +679,7 @@
         <v>-12143.99999999999</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>90322.75</v>
@@ -909,7 +909,7 @@
         <v>-1707.749999999997</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>107590</v>
@@ -1185,7 +1185,7 @@
         <v>-9867.000000000009</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>124857.25</v>
@@ -1323,7 +1323,7 @@
         <v>-1707.749999999997</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>129221.5</v>
@@ -1415,7 +1415,7 @@
         <v>-3036.000000000003</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>128652.25</v>
@@ -1461,7 +1461,7 @@
         <v>-1707.749999999997</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>126944.5</v>
@@ -1553,7 +1553,7 @@
         <v>-2276.999999999985</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>128083</v>
@@ -1645,7 +1645,7 @@
         <v>-2466.750000000015</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>130360</v>
